--- a/artfynd/A 26325-2023 artfynd.xlsx
+++ b/artfynd/A 26325-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26325-2023 artfynd.xlsx
+++ b/artfynd/A 26325-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679867</v>
       </c>
       <c r="B2" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113678298</v>
       </c>
       <c r="B3" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>113678297</v>
       </c>
       <c r="B4" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>113678299</v>
       </c>
       <c r="B5" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>113678301</v>
       </c>
       <c r="B6" t="n">
-        <v>79382</v>
+        <v>79384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26325-2023 artfynd.xlsx
+++ b/artfynd/A 26325-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679867</v>
       </c>
       <c r="B2" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113678298</v>
       </c>
       <c r="B3" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>113678297</v>
       </c>
       <c r="B4" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>113678299</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>113678301</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>79386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26325-2023 artfynd.xlsx
+++ b/artfynd/A 26325-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679867</v>
       </c>
       <c r="B2" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113678298</v>
       </c>
       <c r="B3" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>113678297</v>
       </c>
       <c r="B4" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>113678299</v>
       </c>
       <c r="B5" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>113678301</v>
       </c>
       <c r="B6" t="n">
-        <v>79386</v>
+        <v>79394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26325-2023 artfynd.xlsx
+++ b/artfynd/A 26325-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679867</v>
       </c>
       <c r="B2" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26325-2023 artfynd.xlsx
+++ b/artfynd/A 26325-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679867</v>
       </c>
       <c r="B2" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113678298</v>
       </c>
       <c r="B3" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>113678297</v>
       </c>
       <c r="B4" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>113678299</v>
       </c>
       <c r="B5" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>113678301</v>
       </c>
       <c r="B6" t="n">
-        <v>79394</v>
+        <v>79395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26325-2023 artfynd.xlsx
+++ b/artfynd/A 26325-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679867</v>
       </c>
       <c r="B2" t="n">
-        <v>92209</v>
+        <v>92211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26325-2023 artfynd.xlsx
+++ b/artfynd/A 26325-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679867</v>
       </c>
       <c r="B2" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113678298</v>
       </c>
       <c r="B3" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>113678297</v>
       </c>
       <c r="B4" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>113678299</v>
       </c>
       <c r="B5" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>113678301</v>
       </c>
       <c r="B6" t="n">
-        <v>79395</v>
+        <v>79396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26325-2023 artfynd.xlsx
+++ b/artfynd/A 26325-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679867</v>
+        <v>113678294</v>
       </c>
       <c r="B2" t="n">
-        <v>92215</v>
+        <v>79440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>637</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nybodvallen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599367</v>
+        <v>599424</v>
       </c>
       <c r="R2" t="n">
-        <v>6873357</v>
+        <v>6873546</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,15 +757,16 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113678298</v>
+        <v>113678295</v>
       </c>
       <c r="B3" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599416</v>
+        <v>599422</v>
       </c>
       <c r="R3" t="n">
-        <v>6873550</v>
+        <v>6873544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113678297</v>
+        <v>113678296</v>
       </c>
       <c r="B4" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599414</v>
+        <v>599422</v>
       </c>
       <c r="R4" t="n">
-        <v>6873551</v>
+        <v>6873550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113678299</v>
+        <v>113678297</v>
       </c>
       <c r="B5" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599415</v>
+        <v>599414</v>
       </c>
       <c r="R5" t="n">
-        <v>6873548</v>
+        <v>6873551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113678301</v>
+        <v>113678298</v>
       </c>
       <c r="B6" t="n">
-        <v>79399</v>
+        <v>79440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599419</v>
+        <v>599416</v>
       </c>
       <c r="R6" t="n">
-        <v>6873553</v>
+        <v>6873550</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,6 +1218,879 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113678299</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79440</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>637</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nybodvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>599415</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6873548</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113678300</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79440</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>637</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nybodvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>599422</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6873555</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113678301</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79440</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>637</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nybodvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>599419</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6873553</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122743049</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79440</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>637</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Renskinns- NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>599438</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6873491</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gran 27 cm i brh. Ca 20 bålar. Men flera högt i trädet.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122743052</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79440</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>637</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Renskinns- NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>599446</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6873501</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt på äldre gran. 33 cm i brh. Hänsyn utökat för arten. Minst 100 bålar!</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113679867</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>658</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nybodvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>599367</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6873357</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>63805140</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gammelbodtjärnarna, svämskog norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>599288</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6873297</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2017-02-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2017-02-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Framförallt talrik på flera tallar, men även på andra träd.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Svämblandskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122743039</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lappberget N, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>599443</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6873491</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 26325-2023 artfynd.xlsx
+++ b/artfynd/A 26325-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678294</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678295</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678296</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678297</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678298</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678299</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678300</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678301</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743049</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743052</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679867</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1994,6 +2054,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63805140</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2095,8 +2160,28 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743039</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>